--- a/public/downloads/RaoResolving2022.xlsx
+++ b/public/downloads/RaoResolving2022.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,13 +169,34 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
     <t>HO</t>
   </si>
   <si>
-    <t>O</t>
+    <t>HO2</t>
   </si>
   <si>
-    <t>HO2</t>
+    <t>O</t>
   </si>
 </sst>
 </file>
@@ -659,10 +682,10 @@
         <v>78</v>
       </c>
       <c r="N3" s="5">
-        <v>509.5290780067444</v>
+        <v>509529.0780067444</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03462180322122337</v>
+        <v>34.62180322122337</v>
       </c>
       <c r="P3" s="5">
         <v>14717</v>
@@ -709,10 +732,10 @@
         <v>78</v>
       </c>
       <c r="N4" s="5">
-        <v>1032.986317396164</v>
+        <v>1032986.317396164</v>
       </c>
       <c r="O4" s="4">
-        <v>0.06062482055262421</v>
+        <v>60.62482055262421</v>
       </c>
       <c r="P4" s="5">
         <v>17039</v>
@@ -759,10 +782,10 @@
         <v>78</v>
       </c>
       <c r="N5" s="5">
-        <v>2114.434054374695</v>
+        <v>2114434.054374695</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1379818620709146</v>
+        <v>137.9818620709146</v>
       </c>
       <c r="P5" s="5">
         <v>15324</v>
@@ -809,10 +832,10 @@
         <v>78</v>
       </c>
       <c r="N6" s="5">
-        <v>1242.503150463104</v>
+        <v>1242503.150463104</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08396993650490668</v>
+        <v>83.96993650490668</v>
       </c>
       <c r="P6" s="5">
         <v>14797</v>
@@ -859,10 +882,10 @@
         <v>78</v>
       </c>
       <c r="N7" s="5">
-        <v>3297.7722260952</v>
+        <v>3297772.2260952</v>
       </c>
       <c r="O7" s="4">
-        <v>0.2637373821253359</v>
+        <v>263.7373821253359</v>
       </c>
       <c r="P7" s="5">
         <v>12504</v>
@@ -909,10 +932,10 @@
         <v>78</v>
       </c>
       <c r="N8" s="5">
-        <v>295.7590477466583</v>
+        <v>295759.0477466583</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01864693573839344</v>
+        <v>18.64693573839344</v>
       </c>
       <c r="P8" s="5">
         <v>15861</v>
@@ -959,10 +982,10 @@
         <v>78</v>
       </c>
       <c r="N9" s="5">
-        <v>538.4380924701691</v>
+        <v>538438.0924701691</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02995816460636338</v>
+        <v>29.95816460636338</v>
       </c>
       <c r="P9" s="5">
         <v>17973</v>
@@ -1009,10 +1032,10 @@
         <v>78</v>
       </c>
       <c r="N10" s="5">
-        <v>1181.079157829285</v>
+        <v>1181079.157829285</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08221350117146628</v>
+        <v>82.21350117146628</v>
       </c>
       <c r="P10" s="5">
         <v>14366</v>
@@ -1059,10 +1082,10 @@
         <v>78</v>
       </c>
       <c r="N11" s="5">
-        <v>561.2479360103607</v>
+        <v>561247.9360103607</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04197501578119518</v>
+        <v>41.97501578119518</v>
       </c>
       <c r="P11" s="5">
         <v>13371</v>
@@ -1109,10 +1132,10 @@
         <v>78</v>
       </c>
       <c r="N12" s="5">
-        <v>316.5199520587921</v>
+        <v>316519.9520587921</v>
       </c>
       <c r="O12" s="4">
-        <v>0.0214488007087343</v>
+        <v>21.4488007087343</v>
       </c>
       <c r="P12" s="5">
         <v>14757</v>
@@ -1159,10 +1182,10 @@
         <v>78</v>
       </c>
       <c r="N13" s="5">
-        <v>1073.031743049622</v>
+        <v>1073031.743049622</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07280220795505947</v>
+        <v>72.80220795505947</v>
       </c>
       <c r="P13" s="5">
         <v>14739</v>
@@ -1209,10 +1232,10 @@
         <v>78</v>
       </c>
       <c r="N14" s="5">
-        <v>6388.248245716095</v>
+        <v>6388248.245716095</v>
       </c>
       <c r="O14" s="4">
-        <v>0.383149298009722</v>
+        <v>383.149298009722</v>
       </c>
       <c r="P14" s="5">
         <v>16673</v>
@@ -1259,10 +1282,10 @@
         <v>78</v>
       </c>
       <c r="N15" s="5">
-        <v>4550.960397720337</v>
+        <v>4550960.397720337</v>
       </c>
       <c r="O15" s="4">
-        <v>0.3690067621600857</v>
+        <v>369.0067621600857</v>
       </c>
       <c r="P15" s="5">
         <v>12333</v>
@@ -1309,10 +1332,10 @@
         <v>78</v>
       </c>
       <c r="N16" s="5">
-        <v>1918.17519903183</v>
+        <v>1918175.19903183</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1001448887455273</v>
+        <v>100.1448887455273</v>
       </c>
       <c r="P16" s="5">
         <v>19154</v>
@@ -1359,10 +1382,10 @@
         <v>78</v>
       </c>
       <c r="N17" s="5">
-        <v>1132.597261190414</v>
+        <v>1132597.261190414</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1035943712787354</v>
+        <v>103.5943712787354</v>
       </c>
       <c r="P17" s="5">
         <v>10933</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,132 +1497,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3210695570549153</v>
+        <v>0.3802748974524792</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3127335485032338</v>
+        <v>0.3837426829471419</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3606656742274101</v>
+        <v>0.4369481226018091</v>
       </c>
       <c r="E3" s="4">
-        <v>85.32443746729469</v>
+        <v>82.89638932496067</v>
       </c>
       <c r="F3" s="4">
-        <v>86.46962657029687</v>
+        <v>80.84279814145566</v>
       </c>
       <c r="G3" s="5">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I3" s="5">
+        <v>3</v>
+      </c>
+      <c r="J3" s="5">
         <v>2</v>
       </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3026103696103103</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2326696075162164</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2446520267788118</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4923663265325734</v>
+        <v>0.6659751889203377</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4977439973555308</v>
+        <v>0.4159649382937791</v>
       </c>
       <c r="D4" s="4">
-        <v>0.457052543447778</v>
+        <v>0.5789553904401686</v>
       </c>
       <c r="E4" s="4">
-        <v>85.86211407639981</v>
+        <v>72.34955520669831</v>
       </c>
       <c r="F4" s="4">
-        <v>85.78084667010647</v>
+        <v>56.69075890552377</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J4" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.3715930433798952</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6979898756815204</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3057621166144613</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.416725868238513</v>
+        <v>0.5366122255279253</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2794447480392133</v>
+        <v>0.5047357605240143</v>
       </c>
       <c r="D5" s="4">
-        <v>0.316695777424172</v>
+        <v>0.5030381711836849</v>
       </c>
       <c r="E5" s="4">
-        <v>83.26792255363668</v>
+        <v>82.51831501831495</v>
       </c>
       <c r="F5" s="4">
-        <v>79.48029599036335</v>
+        <v>81.15771812080482</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I5" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="5">
         <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.4526805599656172</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4274997394051292</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3507720854854241</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,132 +1797,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3537883631535375</v>
+        <v>0.5322412814151577</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3738286920312458</v>
+        <v>0.4747519298598852</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4206925176447899</v>
+        <v>0.5372801002432838</v>
       </c>
       <c r="E3" s="4">
-        <v>86.10020931449506</v>
+        <v>82.21742543171106</v>
       </c>
       <c r="F3" s="4">
-        <v>84.81844777146721</v>
+        <v>81.51049733264692</v>
       </c>
       <c r="G3" s="5">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>3</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
         <v>2</v>
       </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.4195448307488877</v>
+      </c>
+      <c r="O3" s="5">
+        <v>22</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3071672268126578</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2306159322159162</v>
+      </c>
+      <c r="R3" s="5">
+        <v>22</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5493348852000017</v>
+        <v>0.8036578287662982</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5281061678835176</v>
+        <v>0.7660665347472804</v>
       </c>
       <c r="D4" s="4">
-        <v>0.557758653335897</v>
+        <v>0.8444191738565431</v>
       </c>
       <c r="E4" s="4">
-        <v>85.91313448456299</v>
+        <v>75.74175824175823</v>
       </c>
       <c r="F4" s="4">
-        <v>85.26157287902373</v>
+        <v>67.08569953536549</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.7660665347472804</v>
+      </c>
+      <c r="O4" s="5">
+        <v>13</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5958766452493431</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2736296775152562</v>
+      </c>
+      <c r="R4" s="5">
+        <v>13</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6248968258090435</v>
+        <v>0.9105918246274854</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3702517710950701</v>
+        <v>0.8313381454730979</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4428830875508046</v>
+        <v>0.763524309905429</v>
       </c>
       <c r="E5" s="4">
-        <v>78.82391418105679</v>
+        <v>81.233647305076</v>
       </c>
       <c r="F5" s="4">
-        <v>67.43761831009965</v>
+        <v>79.32971949750457</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I5" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>4</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.7318667912591142</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6497814432014807</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4395251836554008</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,34 +2097,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3021739760884882</v>
+        <v>0.3210695570549153</v>
       </c>
       <c r="C3" s="4">
-        <v>0.286160156884763</v>
+        <v>0.3127335485032338</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3312391082296015</v>
+        <v>0.3606656742274101</v>
       </c>
       <c r="E3" s="4">
-        <v>85.24856096284672</v>
+        <v>85.32443746729469</v>
       </c>
       <c r="F3" s="4">
-        <v>85.69609361555626</v>
+        <v>86.46962657029687</v>
       </c>
       <c r="G3" s="5">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
         <v>1</v>
@@ -1927,91 +2156,145 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1536160055651393</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2619864779914002</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2659808511573218</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5219938997864665</v>
+        <v>0.416725868238513</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3628868543778604</v>
+        <v>0.2794447480392133</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4394574100075067</v>
+        <v>0.316695777424172</v>
       </c>
       <c r="E4" s="4">
-        <v>84.25170068027217</v>
+        <v>83.26792255363668</v>
       </c>
       <c r="F4" s="4">
-        <v>84.47083118224249</v>
+        <v>79.48029599036335</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.08528878977759848</v>
+      </c>
+      <c r="O4" s="5">
+        <v>19</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4046499347540066</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2584309027563308</v>
+      </c>
+      <c r="R4" s="5">
+        <v>19</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.597285485664253</v>
+        <v>0.4923663265325734</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2659936897433092</v>
+        <v>0.4977439973555308</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2782686461076513</v>
+        <v>0.457052543447778</v>
       </c>
       <c r="E5" s="4">
-        <v>78.60936682365227</v>
+        <v>85.86211407639981</v>
       </c>
       <c r="F5" s="4">
-        <v>70.07442780932905</v>
+        <v>85.78084667010647</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I5" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.2513749431599299</v>
+      </c>
+      <c r="O5" s="5">
+        <v>22</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4509364718605794</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4382679980930672</v>
+      </c>
+      <c r="R5" s="5">
+        <v>22</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,34 +2397,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2598737163247478</v>
+        <v>0.3537883631535375</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2581170456540948</v>
+        <v>0.3738286920312458</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2966251478513726</v>
+        <v>0.4206925176447899</v>
       </c>
       <c r="E3" s="4">
-        <v>82.65306122448983</v>
+        <v>86.10020931449506</v>
       </c>
       <c r="F3" s="4">
-        <v>84.85802787816165</v>
+        <v>84.81844777146721</v>
       </c>
       <c r="G3" s="5">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
         <v>1</v>
@@ -2140,34 +2456,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.161811584594077</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.299536790622193</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3232719377967728</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5220548119968773</v>
+        <v>0.6248968258090435</v>
       </c>
       <c r="C4" s="4">
-        <v>0.432175082729706</v>
+        <v>0.3702517710950701</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4489502297457111</v>
+        <v>0.4428830875508046</v>
       </c>
       <c r="E4" s="4">
-        <v>79.97645211930903</v>
+        <v>78.82391418105679</v>
       </c>
       <c r="F4" s="4">
-        <v>79.86319050077365</v>
+        <v>67.43761831009965</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J4" s="5">
         <v>4</v>
@@ -2181,50 +2515,86 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2350247644585798</v>
+      </c>
+      <c r="O4" s="5">
+        <v>13</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6446577391193015</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2832218014686587</v>
+      </c>
+      <c r="R4" s="5">
+        <v>13</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5519820478346571</v>
+        <v>0.5493348852000017</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2616719805690436</v>
+        <v>0.5281061678835176</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3552162762141343</v>
+        <v>0.557758653335897</v>
       </c>
       <c r="E5" s="4">
-        <v>76.23888016745131</v>
+        <v>85.91313448456299</v>
       </c>
       <c r="F5" s="4">
-        <v>69.60505937015871</v>
+        <v>85.26157287902373</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I5" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" s="5">
         <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3987193783200783</v>
+      </c>
+      <c r="O5" s="5">
+        <v>22</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4490875447755915</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4211293715656467</v>
+      </c>
+      <c r="R5" s="5">
+        <v>22</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,132 +2697,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.341896331326669</v>
+        <v>0.3021739760884882</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2706862905868618</v>
+        <v>0.286160156884763</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3515294263336892</v>
+        <v>0.3312391082296015</v>
       </c>
       <c r="E3" s="4">
-        <v>78.87362637362652</v>
+        <v>85.24856096284672</v>
       </c>
       <c r="F3" s="4">
-        <v>76.88995009464749</v>
+        <v>85.69609361555626</v>
       </c>
       <c r="G3" s="5">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.07951469339842158</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2715914017044799</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2596552590852891</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5043370076827803</v>
+        <v>0.597285485664253</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3473152794514264</v>
+        <v>0.2659936897433092</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3654057486184291</v>
+        <v>0.2782686461076513</v>
       </c>
       <c r="E4" s="4">
-        <v>78.95735217163806</v>
+        <v>78.60936682365227</v>
       </c>
       <c r="F4" s="4">
-        <v>76.02693168129257</v>
+        <v>70.07442780932905</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J4" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.08256383040490789</v>
+      </c>
+      <c r="O4" s="5">
+        <v>14</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5782322940323511</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2659936897433092</v>
+      </c>
+      <c r="R4" s="5">
+        <v>14</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4649229682357545</v>
+        <v>0.5219938997864665</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3068643714937596</v>
+        <v>0.3628868543778604</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3464221901259456</v>
+        <v>0.4394574100075067</v>
       </c>
       <c r="E5" s="4">
-        <v>74.01753008895896</v>
+        <v>84.25170068027217</v>
       </c>
       <c r="F5" s="4">
-        <v>62.60454310789951</v>
+        <v>84.47083118224249</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I5" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.224990091013383</v>
+      </c>
+      <c r="O5" s="5">
+        <v>23</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4926427854672435</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3199251559729395</v>
+      </c>
+      <c r="R5" s="5">
+        <v>23</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2905,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2924,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2966,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,81 +2997,117 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2527543032835963</v>
+        <v>0.2598737163247478</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2530736720870814</v>
+        <v>0.2581170456540948</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2441448201340782</v>
+        <v>0.2966251478513726</v>
       </c>
       <c r="E3" s="4">
-        <v>83.19989534275228</v>
+        <v>82.65306122448983</v>
       </c>
       <c r="F3" s="4">
-        <v>83.22922044398534</v>
+        <v>84.85802787816165</v>
       </c>
       <c r="G3" s="5">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.06604912907716336</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2760509542112405</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2798339432470729</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4417650854369242</v>
+        <v>0.5519820478346571</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4261453307591506</v>
+        <v>0.2616719805690436</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4010978967419974</v>
+        <v>0.3552162762141343</v>
       </c>
       <c r="E4" s="4">
-        <v>84.00313971742506</v>
+        <v>76.23888016745131</v>
       </c>
       <c r="F4" s="4">
-        <v>83.62416107382474</v>
+        <v>69.60505937015871</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
         <v>3</v>
@@ -2607,40 +3115,58 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1472263369782988</v>
+      </c>
+      <c r="O4" s="5">
+        <v>13</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.573648256873668</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2257286787356738</v>
+      </c>
+      <c r="R4" s="5">
+        <v>13</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6437936440710388</v>
+        <v>0.5220548119968773</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4320348461924566</v>
+        <v>0.432175082729706</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4499724224827534</v>
+        <v>0.4489502297457111</v>
       </c>
       <c r="E5" s="4">
-        <v>79.58006279434819</v>
+        <v>79.97645211930903</v>
       </c>
       <c r="F5" s="4">
-        <v>76.21579762519205</v>
+        <v>79.86319050077365</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I5" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
         <v>3</v>
@@ -2648,9 +3174,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.2505847407534945</v>
+      </c>
+      <c r="O5" s="5">
+        <v>22</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5239881986229101</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3888991322416551</v>
+      </c>
+      <c r="R5" s="5">
+        <v>22</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3224,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3266,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,34 +3297,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3752238113656216</v>
+        <v>0.341896331326669</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2682539170285193</v>
+        <v>0.2706862905868618</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3655545169357405</v>
+        <v>0.3515294263336892</v>
       </c>
       <c r="E3" s="4">
-        <v>78.16849816849829</v>
+        <v>78.87362637362652</v>
       </c>
       <c r="F3" s="4">
-        <v>76.73851316468676</v>
+        <v>76.88995009464749</v>
       </c>
       <c r="G3" s="5">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" s="5">
         <v>2</v>
@@ -2779,91 +3356,145 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.01104445124620772</v>
+      </c>
+      <c r="O3" s="5">
+        <v>20</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3435954776722395</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2728951808361034</v>
+      </c>
+      <c r="R3" s="5">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.524477340354051</v>
+        <v>0.4649229682357545</v>
       </c>
       <c r="C4" s="4">
-        <v>0.319350290474881</v>
+        <v>0.3068643714937596</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3485413948413466</v>
+        <v>0.3464221901259456</v>
       </c>
       <c r="E4" s="4">
-        <v>76.74254317111459</v>
+        <v>74.01753008895896</v>
       </c>
       <c r="F4" s="4">
-        <v>73.82292204439788</v>
+        <v>62.60454310789951</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J4" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1797345993024008</v>
+      </c>
+      <c r="O4" s="5">
+        <v>14</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5208721368609095</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3080644850533897</v>
+      </c>
+      <c r="R4" s="5">
+        <v>14</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4687962346778689</v>
+        <v>0.5043370076827803</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3269265003132804</v>
+        <v>0.3473152794514264</v>
       </c>
       <c r="D5" s="4">
-        <v>0.420015258561092</v>
+        <v>0.3654057486184291</v>
       </c>
       <c r="E5" s="4">
-        <v>72.16117216117198</v>
+        <v>78.95735217163806</v>
       </c>
       <c r="F5" s="4">
-        <v>60.330838065737</v>
+        <v>76.02693168129257</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I5" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>5</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.0992801675499464</v>
+      </c>
+      <c r="O5" s="5">
+        <v>20</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.471933713457921</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3250470304690986</v>
+      </c>
+      <c r="R5" s="5">
+        <v>20</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3505,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3524,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3566,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,75 +3597,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2297366177754065</v>
+        <v>0.2527543032835963</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2421150136065193</v>
+        <v>0.2530736720870814</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2763711184877573</v>
+        <v>0.2441448201340782</v>
       </c>
       <c r="E3" s="4">
-        <v>85.46964939822084</v>
+        <v>83.19989534275228</v>
       </c>
       <c r="F3" s="4">
-        <v>85.6328514885556</v>
+        <v>83.22922044398534</v>
       </c>
       <c r="G3" s="5">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I3" s="5">
         <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1781691255715301</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2951492903569355</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2843658041541283</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3857497429019184</v>
+        <v>0.6437936440710388</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3198122286416351</v>
+        <v>0.4320348461924566</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3692950040570849</v>
+        <v>0.4499724224827534</v>
       </c>
       <c r="E4" s="4">
-        <v>85.81109366823659</v>
+        <v>79.58006279434819</v>
       </c>
       <c r="F4" s="4">
-        <v>85.18198244708317</v>
+        <v>76.21579762519205</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J4" s="5">
         <v>3</v>
@@ -3033,50 +3715,86 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.4320348461924566</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4638737735806657</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2460047656477659</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4893349786788029</v>
+        <v>0.4417650854369242</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3011715859484529</v>
+        <v>0.4261453307591506</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3156544233168307</v>
+        <v>0.4010978967419974</v>
       </c>
       <c r="E5" s="4">
-        <v>81.54892726321314</v>
+        <v>84.00313971742506</v>
       </c>
       <c r="F5" s="4">
-        <v>77.56066081569269</v>
+        <v>83.62416107382474</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I5" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.04426085205641011</v>
+      </c>
+      <c r="O5" s="5">
+        <v>23</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4349557235820919</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4165234063990615</v>
+      </c>
+      <c r="R5" s="5">
+        <v>23</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3805,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.3752238113656216</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2682539170285193</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3655545169357405</v>
+      </c>
+      <c r="E3" s="4">
+        <v>78.16849816849829</v>
+      </c>
+      <c r="F3" s="4">
+        <v>76.73851316468676</v>
+      </c>
+      <c r="G3" s="5">
+        <v>26</v>
+      </c>
+      <c r="H3" s="5">
+        <v>21</v>
+      </c>
+      <c r="I3" s="5">
+        <v>3</v>
+      </c>
+      <c r="J3" s="5">
+        <v>2</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.1521323315332168</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3723292862847845</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2719146160490646</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4687962346778689</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3269265003132804</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.420015258561092</v>
+      </c>
+      <c r="E4" s="4">
+        <v>72.16117216117198</v>
+      </c>
+      <c r="F4" s="4">
+        <v>60.330838065737</v>
+      </c>
+      <c r="G4" s="5">
+        <v>26</v>
+      </c>
+      <c r="H4" s="5">
+        <v>12</v>
+      </c>
+      <c r="I4" s="5">
+        <v>9</v>
+      </c>
+      <c r="J4" s="5">
+        <v>5</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>4</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.2565488834579965</v>
+      </c>
+      <c r="O4" s="5">
+        <v>12</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5292393769020068</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3310199618083633</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.524477340354051</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.319350290474881</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3485413948413466</v>
+      </c>
+      <c r="E5" s="4">
+        <v>76.74254317111459</v>
+      </c>
+      <c r="F5" s="4">
+        <v>73.82292204439788</v>
+      </c>
+      <c r="G5" s="5">
+        <v>26</v>
+      </c>
+      <c r="H5" s="5">
+        <v>19</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>7</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>6</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.01230149299580389</v>
+      </c>
+      <c r="O5" s="5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5197881231583072</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3161707019427589</v>
+      </c>
+      <c r="R5" s="5">
+        <v>19</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2297366177754065</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2421150136065193</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2763711184877573</v>
+      </c>
+      <c r="E3" s="4">
+        <v>85.46964939822084</v>
+      </c>
+      <c r="F3" s="4">
+        <v>85.6328514885556</v>
+      </c>
+      <c r="G3" s="5">
+        <v>26</v>
+      </c>
+      <c r="H3" s="5">
+        <v>22</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>2</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.04256701054711633</v>
+      </c>
+      <c r="O3" s="5">
+        <v>22</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2395597740555102</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2537241983011874</v>
+      </c>
+      <c r="R3" s="5">
+        <v>22</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4893349786788029</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3011715859484529</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3156544233168307</v>
+      </c>
+      <c r="E4" s="4">
+        <v>81.54892726321314</v>
+      </c>
+      <c r="F4" s="4">
+        <v>77.56066081569269</v>
+      </c>
+      <c r="G4" s="5">
+        <v>26</v>
+      </c>
+      <c r="H4" s="5">
+        <v>19</v>
+      </c>
+      <c r="I4" s="5">
+        <v>5</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2430980938497209</v>
+      </c>
+      <c r="O4" s="5">
+        <v>19</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4160177598554617</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.213637396708603</v>
+      </c>
+      <c r="R4" s="5">
+        <v>19</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3857497429019184</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3198122286416351</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3692950040570849</v>
+      </c>
+      <c r="E5" s="4">
+        <v>85.81109366823659</v>
+      </c>
+      <c r="F5" s="4">
+        <v>85.18198244708317</v>
+      </c>
+      <c r="G5" s="5">
+        <v>26</v>
+      </c>
+      <c r="H5" s="5">
+        <v>21</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.1009055627885135</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3858580268537909</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3055312140884514</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>71.7948717948718</v>
+      </c>
+      <c r="C3" s="3">
+        <v>14.1025641025641</v>
+      </c>
+      <c r="D3" s="3">
+        <v>14.1025641025641</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="F3" s="3">
+        <v>12.82051282051282</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.4346557514038115</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2974715002274481</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.3616295911716735</v>
+      </c>
+      <c r="K3" s="4">
+        <v>80.81371009942434</v>
+      </c>
+      <c r="L3" s="4">
+        <v>76.0270750874775</v>
+      </c>
+      <c r="M3" s="5">
+        <v>78</v>
+      </c>
+      <c r="N3" s="5">
+        <v>509529.0780067444</v>
+      </c>
+      <c r="O3" s="4">
+        <v>34.62180322122337</v>
+      </c>
+      <c r="P3" s="5">
+        <v>14717</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>67.94871794871796</v>
+      </c>
+      <c r="C4" s="3">
+        <v>19.23076923076923</v>
+      </c>
+      <c r="D4" s="3">
+        <v>12.82051282051282</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3.846153846153846</v>
+      </c>
+      <c r="F4" s="3">
+        <v>8.974358974358974</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.709120933768896</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.3904897352852527</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.4117625591438035</v>
+      </c>
+      <c r="K4" s="4">
+        <v>79.93197278911569</v>
+      </c>
+      <c r="L4" s="4">
+        <v>76.07941834451907</v>
+      </c>
+      <c r="M4" s="5">
+        <v>78</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1032986.317396164</v>
+      </c>
+      <c r="O4" s="4">
+        <v>60.62482055262421</v>
+      </c>
+      <c r="P4" s="5">
+        <v>17039</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>73.07692307692307</v>
+      </c>
+      <c r="C5" s="3">
+        <v>5.128205128205128</v>
+      </c>
+      <c r="D5" s="3">
+        <v>21.7948717948718</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="F5" s="3">
+        <v>19.23076923076923</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.4636172927940696</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.3321557712188074</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.3712052731444372</v>
+      </c>
+      <c r="K5" s="4">
+        <v>80.43607186464357</v>
+      </c>
+      <c r="L5" s="4">
+        <v>75.85541788561964</v>
+      </c>
+      <c r="M5" s="5">
+        <v>78</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2114434.054374695</v>
+      </c>
+      <c r="O5" s="4">
+        <v>137.9818620709146</v>
+      </c>
+      <c r="P5" s="5">
+        <v>15324</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>76.92307692307693</v>
+      </c>
+      <c r="C6" s="3">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="D6" s="3">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3.846153846153846</v>
+      </c>
+      <c r="F6" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.4799624555715596</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.336617713111858</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.3155436161861834</v>
+      </c>
+      <c r="K6" s="4">
+        <v>83.43275771847172</v>
+      </c>
+      <c r="L6" s="4">
+        <v>80.56588080078055</v>
+      </c>
+      <c r="M6" s="5">
+        <v>78</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1242503.150463104</v>
+      </c>
+      <c r="O6" s="4">
+        <v>83.96993650490668</v>
+      </c>
+      <c r="P6" s="5">
+        <v>14797</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>79.48717948717949</v>
+      </c>
+      <c r="C7" s="3">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="D7" s="3">
+        <v>8.974358974358974</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>8.974358974358974</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.3705752886956341</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.2895619904959005</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.3124033887650277</v>
+      </c>
+      <c r="K7" s="4">
+        <v>83.45368916797473</v>
+      </c>
+      <c r="L7" s="4">
+        <v>80.83734870647541</v>
+      </c>
+      <c r="M7" s="5">
+        <v>78</v>
+      </c>
+      <c r="N7" s="5">
+        <v>3297772.2260952</v>
+      </c>
+      <c r="O7" s="4">
+        <v>263.7373821253359</v>
+      </c>
+      <c r="P7" s="5">
+        <v>12504</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>62.82051282051282</v>
+      </c>
+      <c r="C8" s="3">
+        <v>24.35897435897436</v>
+      </c>
+      <c r="D8" s="3">
+        <v>12.82051282051282</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="F8" s="3">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.4527197408676218</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.2988620647724527</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.3264463468186345</v>
+      </c>
+      <c r="K8" s="4">
+        <v>79.2547531833245</v>
+      </c>
+      <c r="L8" s="4">
+        <v>72.89709172259595</v>
+      </c>
+      <c r="M8" s="5">
+        <v>78</v>
+      </c>
+      <c r="N8" s="5">
+        <v>295759.0477466583</v>
+      </c>
+      <c r="O8" s="4">
+        <v>18.64693573839344</v>
+      </c>
+      <c r="P8" s="5">
+        <v>15861</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>71.7948717948718</v>
+      </c>
+      <c r="C9" s="3">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="D9" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="F9" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.5176084384211607</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.318942235235927</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.330371639482937</v>
+      </c>
+      <c r="K9" s="4">
+        <v>79.73094365951498</v>
+      </c>
+      <c r="L9" s="4">
+        <v>75.97530545517185</v>
+      </c>
+      <c r="M9" s="5">
+        <v>78</v>
+      </c>
+      <c r="N9" s="5">
+        <v>538438.0924701691</v>
+      </c>
+      <c r="O9" s="4">
+        <v>29.95816460636338</v>
+      </c>
+      <c r="P9" s="5">
+        <v>17973</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>82.05128205128204</v>
+      </c>
+      <c r="C10" s="3">
+        <v>8.974358974358974</v>
+      </c>
+      <c r="D10" s="3">
+        <v>8.974358974358974</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="F10" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.372524294868662</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.3229631669849401</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.3234314125636826</v>
+      </c>
+      <c r="K10" s="4">
+        <v>84.81815803244361</v>
+      </c>
+      <c r="L10" s="4">
+        <v>83.91025641025593</v>
+      </c>
+      <c r="M10" s="5">
+        <v>78</v>
+      </c>
+      <c r="N10" s="5">
+        <v>1181079.157829285</v>
+      </c>
+      <c r="O10" s="4">
+        <v>82.21350117146628</v>
+      </c>
+      <c r="P10" s="5">
+        <v>14366</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>74.35897435897436</v>
+      </c>
+      <c r="C11" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="D11" s="3">
+        <v>10.25641025641026</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2.564102564102564</v>
+      </c>
+      <c r="F11" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.4644273581723621</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.3514135200493544</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.3895025109867233</v>
+      </c>
+      <c r="K11" s="4">
+        <v>83.61241932670536</v>
+      </c>
+      <c r="L11" s="4">
+        <v>79.17254632019764</v>
+      </c>
+      <c r="M11" s="5">
+        <v>78</v>
+      </c>
+      <c r="N11" s="5">
+        <v>561247.9360103607</v>
+      </c>
+      <c r="O11" s="4">
+        <v>41.97501578119518</v>
+      </c>
+      <c r="P11" s="5">
+        <v>13371</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>78.2051282051282</v>
+      </c>
+      <c r="C12" s="3">
+        <v>12.82051282051282</v>
+      </c>
+      <c r="D12" s="3">
+        <v>8.974358974358974</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="F12" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.4474888270680248</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.2838346960955881</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.3295102734661871</v>
+      </c>
+      <c r="K12" s="4">
+        <v>82.70320948892387</v>
+      </c>
+      <c r="L12" s="4">
+        <v>80.0804508690408</v>
+      </c>
+      <c r="M12" s="5">
+        <v>78</v>
+      </c>
+      <c r="N12" s="5">
+        <v>316519.9520587921</v>
+      </c>
+      <c r="O12" s="4">
+        <v>21.4488007087343</v>
+      </c>
+      <c r="P12" s="5">
+        <v>14757</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>75.64102564102564</v>
+      </c>
+      <c r="C13" s="3">
+        <v>12.82051282051282</v>
+      </c>
+      <c r="D13" s="3">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2.564102564102564</v>
+      </c>
+      <c r="F13" s="3">
+        <v>8.974358974358974</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.4578958032359397</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.308580819844236</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.3514945572329351</v>
+      </c>
+      <c r="K13" s="4">
+        <v>79.62279783708311</v>
+      </c>
+      <c r="L13" s="4">
+        <v>78.10875924969935</v>
+      </c>
+      <c r="M13" s="5">
+        <v>78</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1073031.743049622</v>
+      </c>
+      <c r="O13" s="4">
+        <v>72.80220795505947</v>
+      </c>
+      <c r="P13" s="5">
+        <v>14739</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>69.23076923076923</v>
+      </c>
+      <c r="C14" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="D14" s="3">
+        <v>14.1025641025641</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>14.1025641025641</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.4454671093303567</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.3013286484602129</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.3435002697345537</v>
+      </c>
+      <c r="K14" s="4">
+        <v>77.28283621140777</v>
+      </c>
+      <c r="L14" s="4">
+        <v>71.8404749612789</v>
+      </c>
+      <c r="M14" s="5">
+        <v>78</v>
+      </c>
+      <c r="N14" s="5">
+        <v>6388248.245716095</v>
+      </c>
+      <c r="O14" s="4">
+        <v>383.149298009722</v>
+      </c>
+      <c r="P14" s="5">
+        <v>16673</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>79.48717948717949</v>
+      </c>
+      <c r="C15" s="3">
+        <v>8.974358974358974</v>
+      </c>
+      <c r="D15" s="3">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.397992929173231</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.3222549357431434</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.3213914189574074</v>
+      </c>
+      <c r="K15" s="4">
+        <v>82.26103261817541</v>
+      </c>
+      <c r="L15" s="4">
+        <v>81.02305971433439</v>
+      </c>
+      <c r="M15" s="5">
+        <v>78</v>
+      </c>
+      <c r="N15" s="5">
+        <v>4550960.397720337</v>
+      </c>
+      <c r="O15" s="4">
+        <v>369.0067621600857</v>
+      </c>
+      <c r="P15" s="5">
+        <v>12333</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="C16" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="D16" s="3">
+        <v>17.94871794871795</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2.564102564102564</v>
+      </c>
+      <c r="F16" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.4737855954483662</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.3017248041469834</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.3538671018491387</v>
+      </c>
+      <c r="K16" s="4">
+        <v>75.69073783359468</v>
+      </c>
+      <c r="L16" s="4">
+        <v>70.29742442494067</v>
+      </c>
+      <c r="M16" s="5">
+        <v>78</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1918175.19903183</v>
+      </c>
+      <c r="O16" s="4">
+        <v>100.1448887455273</v>
+      </c>
+      <c r="P16" s="5">
+        <v>19154</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>79.48717948717949</v>
+      </c>
+      <c r="C17" s="3">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="D17" s="3">
+        <v>8.974358974358974</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>8.974358974358974</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.3471451869215875</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.2589870709023719</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.3031730357504444</v>
+      </c>
+      <c r="K17" s="4">
+        <v>84.27655677655621</v>
+      </c>
+      <c r="L17" s="4">
+        <v>82.791831583777</v>
+      </c>
+      <c r="M17" s="5">
+        <v>78</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1132597.261190414</v>
+      </c>
+      <c r="O17" s="4">
+        <v>103.5943712787354</v>
+      </c>
+      <c r="P17" s="5">
+        <v>10933</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3206,7 +5382,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>4</v>
@@ -3250,10 +5426,10 @@
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
@@ -3297,7 +5473,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
@@ -3341,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
@@ -3429,7 +5605,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
@@ -3470,7 +5646,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
         <v>9</v>
@@ -3517,7 +5693,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
@@ -3602,10 +5778,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
@@ -3649,7 +5825,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
@@ -3781,7 +5957,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
@@ -3847,9 +6023,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>56</v>
+      </c>
+      <c r="C3" s="5">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5">
+        <v>11</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>4</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>53</v>
+      </c>
+      <c r="C4" s="5">
+        <v>15</v>
+      </c>
+      <c r="D4" s="5">
+        <v>10</v>
+      </c>
+      <c r="E4" s="5">
+        <v>3</v>
+      </c>
+      <c r="F4" s="5">
+        <v>7</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5">
+        <v>3</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>4</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>57</v>
+      </c>
+      <c r="C5" s="5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5">
+        <v>17</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
+        <v>15</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>6</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>60</v>
+      </c>
+      <c r="C6" s="5">
+        <v>9</v>
+      </c>
+      <c r="D6" s="5">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3</v>
+      </c>
+      <c r="F6" s="5">
+        <v>6</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>3</v>
+      </c>
+      <c r="I6" s="5">
+        <v>3</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>3</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>62</v>
+      </c>
+      <c r="C7" s="5">
+        <v>9</v>
+      </c>
+      <c r="D7" s="5">
+        <v>7</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>7</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>4</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>49</v>
+      </c>
+      <c r="C8" s="5">
+        <v>19</v>
+      </c>
+      <c r="D8" s="5">
+        <v>10</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
+        <v>9</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>6</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>56</v>
+      </c>
+      <c r="C9" s="5">
+        <v>9</v>
+      </c>
+      <c r="D9" s="5">
+        <v>13</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <v>12</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5">
+        <v>1</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>9</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>64</v>
+      </c>
+      <c r="C10" s="5">
+        <v>7</v>
+      </c>
+      <c r="D10" s="5">
+        <v>7</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5">
+        <v>6</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5">
+        <v>1</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>1</v>
+      </c>
+      <c r="L10" s="5">
+        <v>5</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>58</v>
+      </c>
+      <c r="C11" s="5">
+        <v>12</v>
+      </c>
+      <c r="D11" s="5">
+        <v>8</v>
+      </c>
+      <c r="E11" s="5">
+        <v>2</v>
+      </c>
+      <c r="F11" s="5">
+        <v>6</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5">
+        <v>2</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>3</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>61</v>
+      </c>
+      <c r="C12" s="5">
+        <v>10</v>
+      </c>
+      <c r="D12" s="5">
+        <v>7</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5">
+        <v>6</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>6</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>59</v>
+      </c>
+      <c r="C13" s="5">
+        <v>10</v>
+      </c>
+      <c r="D13" s="5">
+        <v>9</v>
+      </c>
+      <c r="E13" s="5">
+        <v>2</v>
+      </c>
+      <c r="F13" s="5">
+        <v>7</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>2</v>
+      </c>
+      <c r="I13" s="5">
+        <v>2</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>4</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>54</v>
+      </c>
+      <c r="C14" s="5">
+        <v>13</v>
+      </c>
+      <c r="D14" s="5">
+        <v>11</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>11</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>8</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>62</v>
+      </c>
+      <c r="C15" s="5">
+        <v>7</v>
+      </c>
+      <c r="D15" s="5">
+        <v>9</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>9</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>6</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>52</v>
+      </c>
+      <c r="C16" s="5">
+        <v>12</v>
+      </c>
+      <c r="D16" s="5">
+        <v>14</v>
+      </c>
+      <c r="E16" s="5">
+        <v>2</v>
+      </c>
+      <c r="F16" s="5">
+        <v>12</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>2</v>
+      </c>
+      <c r="I16" s="5">
+        <v>2</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>9</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>62</v>
+      </c>
+      <c r="C17" s="5">
+        <v>9</v>
+      </c>
+      <c r="D17" s="5">
+        <v>7</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>7</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>7</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6791,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6833,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6864,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3538898774720795</v>
@@ -3960,91 +6923,145 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2004704173607698</v>
+      </c>
+      <c r="O3" s="5">
+        <v>22</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2929687360582923</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.288373348475414</v>
+      </c>
+      <c r="R3" s="5">
+        <v>22</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5569192363311177</v>
+        <v>0.6191700477866774</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5665008271850457</v>
+        <v>0.4619329326164479</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5350484272856147</v>
+        <v>0.5349042113247534</v>
       </c>
       <c r="E4" s="4">
-        <v>82.52485609628461</v>
+        <v>77.45421245421227</v>
       </c>
       <c r="F4" s="4">
-        <v>81.00025813112957</v>
+        <v>66.21665806229468</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4526199502244289</v>
+      </c>
+      <c r="O4" s="5">
+        <v>13</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5800881864394752</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1911601418743267</v>
+      </c>
+      <c r="R4" s="5">
+        <v>13</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6191700477866774</v>
+        <v>0.5569192363311177</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4619329326164479</v>
+        <v>0.5665008271850457</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5349042113247534</v>
+        <v>0.5350484272856147</v>
       </c>
       <c r="E5" s="4">
-        <v>77.45421245421227</v>
+        <v>82.52485609628461</v>
       </c>
       <c r="F5" s="4">
-        <v>66.21665806229468</v>
+        <v>81.00025813112957</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I5" s="5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.4916059510887389</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4309103317136674</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3728146905672257</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7072,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7091,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7133,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,10 +7164,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4665927704719097</v>
@@ -4173,91 +7223,143 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3985281152055432</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3003933329732034</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3068322002872887</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7173862571531674</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.7474115722776622</v>
-      </c>
+        <v>2.979351306724209</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.7339467566378898</v>
+        <v>3.943997169303555</v>
       </c>
       <c r="E4" s="4">
-        <v>86.46912611198333</v>
+        <v>67.37310308738843</v>
       </c>
       <c r="F4" s="4">
-        <v>85.66253656857643</v>
+        <v>57.76716572018564</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>7</v>
+      </c>
+      <c r="N4" s="4">
+        <v>4.220041084533372</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.429241110759827</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6210773707571462</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>2.979351306724209</v>
+        <v>0.7173862571531674</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>0.7474115722776622</v>
       </c>
       <c r="D5" s="4">
-        <v>3.943997169303555</v>
+        <v>0.7339467566378898</v>
       </c>
       <c r="E5" s="4">
-        <v>67.37310308738843</v>
+        <v>86.46912611198333</v>
       </c>
       <c r="F5" s="4">
-        <v>57.76716572018564</v>
+        <v>85.66253656857643</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I5" s="5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.6947083700325238</v>
+      </c>
+      <c r="O5" s="5">
+        <v>23</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3977283575736577</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4039684247048145</v>
+      </c>
+      <c r="R5" s="5">
+        <v>23</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7370,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7389,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7431,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7462,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3756430614153065</v>
@@ -4386,91 +7521,145 @@
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.05968238288360524</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3480973462382579</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2565130828885357</v>
+      </c>
+      <c r="R3" s="5">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6502387714563937</v>
+        <v>0.4468644668484157</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5241274484601377</v>
+        <v>0.3002729675692706</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5537097750001835</v>
+        <v>0.2775913112290148</v>
       </c>
       <c r="E4" s="4">
-        <v>80.64102564102539</v>
+        <v>78.2980115122969</v>
       </c>
       <c r="F4" s="4">
-        <v>77.47633797969297</v>
+        <v>71.22397177766361</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>7</v>
+      </c>
+      <c r="K4" s="5">
         <v>1</v>
       </c>
-      <c r="J4" s="5">
-        <v>5</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.02203293764961078</v>
+      </c>
+      <c r="O4" s="5">
+        <v>17</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4451696254907534</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2989769124134111</v>
+      </c>
+      <c r="R4" s="5">
+        <v>17</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4468644668484157</v>
+        <v>0.6502387714563937</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3002729675692706</v>
+        <v>0.5241274484601377</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2775913112290148</v>
+        <v>0.5537097750001835</v>
       </c>
       <c r="E5" s="4">
-        <v>78.2980115122969</v>
+        <v>80.64102564102539</v>
       </c>
       <c r="F5" s="4">
-        <v>71.22397177766361</v>
+        <v>77.47633797969297</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3820196114605438</v>
+      </c>
+      <c r="O5" s="5">
+        <v>20</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5975849066531976</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4360004895336659</v>
+      </c>
+      <c r="R5" s="5">
+        <v>20</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7670,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7689,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7731,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7762,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.367561718417631</v>
@@ -4599,91 +7821,145 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2396624319842395</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2797730439261573</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2586901146927918</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5745985253866758</v>
+        <v>0.6411370150485894</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5430886312879538</v>
+        <v>0.4077687906348918</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5152668515444657</v>
+        <v>0.3743796094794279</v>
       </c>
       <c r="E4" s="4">
-        <v>85.56776556776499</v>
+        <v>79.13396127681828</v>
       </c>
       <c r="F4" s="4">
-        <v>85.15659955257118</v>
+        <v>70.52314575804432</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I4" s="5">
+        <v>6</v>
+      </c>
+      <c r="J4" s="5">
+        <v>5</v>
+      </c>
+      <c r="K4" s="5">
         <v>2</v>
       </c>
-      <c r="J4" s="5">
+      <c r="L4" s="5">
         <v>3</v>
       </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.3042133747795902</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6782266789809671</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3503670408241313</v>
+      </c>
+      <c r="R4" s="5">
+        <v>15</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6411370150485894</v>
+        <v>0.5745985253866758</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4077687906348918</v>
+        <v>0.5430886312879538</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3743796094794279</v>
+        <v>0.5152668515444657</v>
       </c>
       <c r="E5" s="4">
-        <v>79.13396127681828</v>
+        <v>85.56776556776499</v>
       </c>
       <c r="F5" s="4">
-        <v>70.52314575804432</v>
+        <v>85.15659955257118</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I5" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
         <v>2</v>
       </c>
-      <c r="L5" s="5">
-        <v>3</v>
-      </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.4450761873070587</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4818876438075546</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4158568772248811</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7970,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7989,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8031,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +8062,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3105161748481541</v>
@@ -4812,91 +8121,145 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1098226580043683</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.264084007999474</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2550651933707127</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4618496829567255</v>
+        <v>0.4362255796593316</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3985115176389531</v>
+        <v>0.23202736656459</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4254787260492399</v>
+        <v>0.2764127166795961</v>
       </c>
       <c r="E4" s="4">
-        <v>85.53636839351077</v>
+        <v>80.23678702250112</v>
       </c>
       <c r="F4" s="4">
-        <v>85.58294613663668</v>
+        <v>74.65238341077057</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.04771873496634151</v>
+      </c>
+      <c r="O4" s="5">
+        <v>17</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4289925153484248</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2237720173223998</v>
+      </c>
+      <c r="R4" s="5">
+        <v>17</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4362255796593316</v>
+        <v>0.4618496829567255</v>
       </c>
       <c r="C5" s="4">
-        <v>0.23202736656459</v>
+        <v>0.3985115176389531</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2764127166795961</v>
+        <v>0.4254787260492399</v>
       </c>
       <c r="E5" s="4">
-        <v>80.23678702250112</v>
+        <v>85.53636839351077</v>
       </c>
       <c r="F5" s="4">
-        <v>74.65238341077057</v>
+        <v>85.58294613663668</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I5" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1756412389029839</v>
+      </c>
+      <c r="O5" s="5">
+        <v>24</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4186493427390036</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3663479189783363</v>
+      </c>
+      <c r="R5" s="5">
+        <v>24</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8270,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3802748974524792</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3837426829471419</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4369481226018091</v>
-      </c>
-      <c r="E3" s="4">
-        <v>82.89638932496067</v>
-      </c>
-      <c r="F3" s="4">
-        <v>80.84279814145566</v>
-      </c>
-      <c r="G3" s="5">
-        <v>26</v>
-      </c>
-      <c r="H3" s="5">
-        <v>21</v>
-      </c>
-      <c r="I3" s="5">
-        <v>3</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.5366122255279253</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.5047357605240143</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.5030381711836849</v>
-      </c>
-      <c r="E4" s="4">
-        <v>82.51831501831495</v>
-      </c>
-      <c r="F4" s="4">
-        <v>81.15771812080482</v>
-      </c>
-      <c r="G4" s="5">
-        <v>26</v>
-      </c>
-      <c r="H4" s="5">
-        <v>21</v>
-      </c>
-      <c r="I4" s="5">
-        <v>2</v>
-      </c>
-      <c r="J4" s="5">
-        <v>3</v>
-      </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.6659751889203377</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.4159649382937791</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.5789553904401686</v>
-      </c>
-      <c r="E5" s="4">
-        <v>72.34955520669831</v>
-      </c>
-      <c r="F5" s="4">
-        <v>56.69075890552377</v>
-      </c>
-      <c r="G5" s="5">
-        <v>26</v>
-      </c>
-      <c r="H5" s="5">
-        <v>7</v>
-      </c>
-      <c r="I5" s="5">
-        <v>14</v>
-      </c>
-      <c r="J5" s="5">
-        <v>5</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>5</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.5322412814151577</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.4747519298598852</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.5372801002432838</v>
-      </c>
-      <c r="E3" s="4">
-        <v>82.21742543171106</v>
-      </c>
-      <c r="F3" s="4">
-        <v>81.51049733264692</v>
-      </c>
-      <c r="G3" s="5">
-        <v>26</v>
-      </c>
-      <c r="H3" s="5">
-        <v>22</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>3</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.9105918246274854</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.8313381454730979</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.763524309905429</v>
-      </c>
-      <c r="E4" s="4">
-        <v>81.233647305076</v>
-      </c>
-      <c r="F4" s="4">
-        <v>79.32971949750457</v>
-      </c>
-      <c r="G4" s="5">
-        <v>26</v>
-      </c>
-      <c r="H4" s="5">
-        <v>21</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>4</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>4</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.8036578287662982</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.7660665347472804</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.8444191738565431</v>
-      </c>
-      <c r="E5" s="4">
-        <v>75.74175824175823</v>
-      </c>
-      <c r="F5" s="4">
-        <v>67.08569953536549</v>
-      </c>
-      <c r="G5" s="5">
-        <v>26</v>
-      </c>
-      <c r="H5" s="5">
-        <v>13</v>
-      </c>
-      <c r="I5" s="5">
-        <v>7</v>
-      </c>
-      <c r="J5" s="5">
-        <v>6</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>6</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/RaoResolving2022.xlsx
+++ b/public/downloads/RaoResolving2022.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3026103696103103</v>
+        <v>0.3733415999389953</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2326696075162164</v>
+        <v>0.2210314869647345</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2446520267788118</v>
+        <v>0.228257687375413</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3715930433798952</v>
+        <v>0.3950222331688256</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6979898756815204</v>
+        <v>0.7033966117866581</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3057621166144613</v>
+        <v>0.302415089501757</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -1675,16 +1675,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4526805599656172</v>
+        <v>0.6128918619290857</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4274997394051292</v>
+        <v>0.445187427812814</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3507720854854241</v>
+        <v>0.3345255801893509</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -1857,16 +1857,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4195448307488877</v>
+        <v>0.4888609395379433</v>
       </c>
       <c r="O3" s="5">
         <v>22</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3071672268126578</v>
+        <v>0.3025344966173461</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2306159322159162</v>
+        <v>0.2250907215056889</v>
       </c>
       <c r="R3" s="5">
         <v>22</v>
@@ -1916,16 +1916,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.7660665347472804</v>
+        <v>0.6772152798224056</v>
       </c>
       <c r="O4" s="5">
         <v>13</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5958766452493431</v>
+        <v>0.575372509497449</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2736296775152562</v>
+        <v>0.2667949655979581</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -1975,22 +1975,22 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.7318667912591142</v>
+        <v>0.9765310852453126</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6497814432014807</v>
+        <v>0.6869541888296229</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4395251836554008</v>
+        <v>0.3476109234335993</v>
       </c>
       <c r="R5" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2157,16 +2157,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1536160055651393</v>
+        <v>0.3084791486240492</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2619864779914002</v>
+        <v>0.2181300959620156</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2659808511573218</v>
+        <v>0.2267568948026767</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -2216,16 +2216,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.08528878977759848</v>
+        <v>0.1573089074934133</v>
       </c>
       <c r="O4" s="5">
         <v>19</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4046499347540066</v>
+        <v>0.404082085804684</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2584309027563308</v>
+        <v>0.2538633137880045</v>
       </c>
       <c r="R4" s="5">
         <v>19</v>
@@ -2275,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2513749431599299</v>
+        <v>0.4379517305009983</v>
       </c>
       <c r="O5" s="5">
         <v>22</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4509364718605794</v>
+        <v>0.4534883280003189</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4382679980930672</v>
+        <v>0.4243223019544805</v>
       </c>
       <c r="R5" s="5">
         <v>22</v>
@@ -2457,16 +2457,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.161811584594077</v>
+        <v>0.3173618679296624</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.299536790622193</v>
+        <v>0.2815246443945413</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3232719377967728</v>
+        <v>0.2979891001002139</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -2516,16 +2516,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2350247644585798</v>
+        <v>0.309344315217345</v>
       </c>
       <c r="O4" s="5">
         <v>13</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6446577391193015</v>
+        <v>0.663524500942776</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2832218014686587</v>
+        <v>0.2757166680123209</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -2575,16 +2575,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3987193783200783</v>
+        <v>0.5065179524633692</v>
       </c>
       <c r="O5" s="5">
         <v>22</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4490875447755915</v>
+        <v>0.4504293066518933</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4211293715656467</v>
+        <v>0.4104231555637431</v>
       </c>
       <c r="R5" s="5">
         <v>22</v>
@@ -2757,16 +2757,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.07951469339842158</v>
+        <v>0.2118053465722198</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2715914017044799</v>
+        <v>0.2429172145312584</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2596552590852891</v>
+        <v>0.2312843998828207</v>
       </c>
       <c r="R3" s="5">
         <v>24</v>
@@ -2816,13 +2816,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.08256383040490789</v>
+        <v>-0.04108328284914364</v>
       </c>
       <c r="O4" s="5">
         <v>14</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5782322940323511</v>
+        <v>0.5878047280836813</v>
       </c>
       <c r="Q4" s="4">
         <v>0.2659936897433092</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.224990091013383</v>
+        <v>0.2731611849144997</v>
       </c>
       <c r="O5" s="5">
         <v>23</v>
@@ -2884,7 +2884,7 @@
         <v>0.4926427854672435</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3199251559729395</v>
+        <v>0.3178307605859345</v>
       </c>
       <c r="R5" s="5">
         <v>23</v>
@@ -3057,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.06604912907716336</v>
+        <v>0.04793392316648237</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2760509542112405</v>
+        <v>0.2587794664235365</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2798339432470729</v>
+        <v>0.2529371146639091</v>
       </c>
       <c r="R3" s="5">
         <v>24</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1472263369782988</v>
+        <v>0.1594385725342136</v>
       </c>
       <c r="O4" s="5">
         <v>13</v>
       </c>
       <c r="P4" s="4">
-        <v>0.573648256873668</v>
+        <v>0.5764664650788791</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2257286787356738</v>
+        <v>0.2247892760006034</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -3175,13 +3175,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2505847407534945</v>
+        <v>0.2895258480785969</v>
       </c>
       <c r="O5" s="5">
         <v>22</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5239881986229101</v>
+        <v>0.5299791382113875</v>
       </c>
       <c r="Q5" s="4">
         <v>0.3888991322416551</v>
@@ -3357,16 +3357,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.01104445124620772</v>
+        <v>-0.10031407307728</v>
       </c>
       <c r="O3" s="5">
         <v>20</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3435954776722395</v>
+        <v>0.3353261608833273</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2728951808361034</v>
+        <v>0.2567694091158025</v>
       </c>
       <c r="R3" s="5">
         <v>20</v>
@@ -3416,16 +3416,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1797345993024008</v>
+        <v>0.08566690219249473</v>
       </c>
       <c r="O4" s="5">
         <v>14</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5208721368609095</v>
+        <v>0.487173033286957</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3080644850533897</v>
+        <v>0.2992334053359959</v>
       </c>
       <c r="R4" s="5">
         <v>14</v>
@@ -3475,16 +3475,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.0992801675499464</v>
+        <v>-0.1938389743877322</v>
       </c>
       <c r="O5" s="5">
         <v>20</v>
       </c>
       <c r="P5" s="4">
-        <v>0.471933713457921</v>
+        <v>0.4514352629429711</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3250470304690986</v>
+        <v>0.3173108061672208</v>
       </c>
       <c r="R5" s="5">
         <v>20</v>
@@ -3657,16 +3657,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1781691255715301</v>
+        <v>-0.04782816749213126</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2951492903569355</v>
+        <v>0.249221635061789</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2843658041541283</v>
+        <v>0.2464223605985518</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -3716,16 +3716,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4320348461924566</v>
+        <v>-0.4285214315379378</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4638737735806657</v>
+        <v>0.4640662575545458</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2460047656477659</v>
+        <v>0.2458924186484239</v>
       </c>
       <c r="R4" s="5">
         <v>18</v>
@@ -3775,16 +3775,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.04426085205641011</v>
+        <v>0.1804829187664332</v>
       </c>
       <c r="O5" s="5">
         <v>23</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4349557235820919</v>
+        <v>0.4303537836172551</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4165234063990615</v>
+        <v>0.4053985148427232</v>
       </c>
       <c r="R5" s="5">
         <v>23</v>
@@ -3957,16 +3957,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1521323315332168</v>
+        <v>0.04304420104148221</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3723292862847845</v>
+        <v>0.3685690424294024</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2719146160490646</v>
+        <v>0.2620644031570804</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2565488834579965</v>
+        <v>0.1253381213176192</v>
       </c>
       <c r="O4" s="5">
         <v>12</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5292393769020068</v>
+        <v>0.4760350322167885</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3310199618083633</v>
+        <v>0.2882048052948014</v>
       </c>
       <c r="R4" s="5">
         <v>12</v>
@@ -4075,16 +4075,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.01230149299580389</v>
+        <v>-0.058125549504072</v>
       </c>
       <c r="O5" s="5">
         <v>19</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5197881231583072</v>
+        <v>0.5064840924332336</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3161707019427589</v>
+        <v>0.3100241484527287</v>
       </c>
       <c r="R5" s="5">
         <v>19</v>
@@ -4257,16 +4257,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.04256701054711633</v>
+        <v>0.08980317500524038</v>
       </c>
       <c r="O3" s="5">
         <v>22</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2395597740555102</v>
+        <v>0.2153416082729618</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2537241983011874</v>
+        <v>0.2251027296490846</v>
       </c>
       <c r="R3" s="5">
         <v>22</v>
@@ -4316,16 +4316,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2430980938497209</v>
+        <v>-0.3097916322863057</v>
       </c>
       <c r="O4" s="5">
         <v>19</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4160177598554617</v>
+        <v>0.4095585551406219</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.213637396708603</v>
+        <v>0.2083086712270634</v>
       </c>
       <c r="R4" s="5">
         <v>19</v>
@@ -4375,16 +4375,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1009055627885135</v>
+        <v>0.1432348014191867</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3858580268537909</v>
+        <v>0.3891141221330734</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3055312140884514</v>
+        <v>0.3035155360584194</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -4521,13 +4521,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.4346557514038115</v>
+        <v>0.4357705594816127</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2974715002274481</v>
+        <v>0.2930387599811693</v>
       </c>
       <c r="J3" s="4">
-        <v>0.3616295911716735</v>
+        <v>0.3593273947566307</v>
       </c>
       <c r="K3" s="4">
         <v>80.81371009942434</v>
@@ -4571,13 +4571,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.709120933768896</v>
+        <v>0.6877954049169909</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3904897352852527</v>
+        <v>0.3839999196131429</v>
       </c>
       <c r="J4" s="4">
-        <v>0.4117625591438035</v>
+        <v>0.4086794756008737</v>
       </c>
       <c r="K4" s="4">
         <v>79.93197278911569</v>
@@ -4621,13 +4621,13 @@
         <v>1.282051282051282</v>
       </c>
       <c r="H5" s="4">
-        <v>0.4636172927940696</v>
+        <v>0.4467500820118727</v>
       </c>
       <c r="I5" s="4">
-        <v>0.3321557712188074</v>
+        <v>0.305338279815722</v>
       </c>
       <c r="J5" s="4">
-        <v>0.3712052731444372</v>
+        <v>0.3542072948355608</v>
       </c>
       <c r="K5" s="4">
         <v>80.43607186464357</v>
@@ -4671,13 +4671,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.4799624555715596</v>
+        <v>0.4824436202018181</v>
       </c>
       <c r="I6" s="4">
-        <v>0.336617713111858</v>
+        <v>0.3323657909934913</v>
       </c>
       <c r="J6" s="4">
-        <v>0.3155436161861834</v>
+        <v>0.3175912719544248</v>
       </c>
       <c r="K6" s="4">
         <v>83.43275771847172</v>
@@ -4721,13 +4721,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.3705752886956341</v>
+        <v>0.3594834660569416</v>
       </c>
       <c r="I7" s="4">
-        <v>0.2895619904959005</v>
+        <v>0.2801965316289722</v>
       </c>
       <c r="J7" s="4">
-        <v>0.3124033887650277</v>
+        <v>0.2903599582036307</v>
       </c>
       <c r="K7" s="4">
         <v>83.45368916797473</v>
@@ -4771,13 +4771,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.4527197408676218</v>
+        <v>0.4565385088547355</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2988620647724527</v>
+        <v>0.2843949845994355</v>
       </c>
       <c r="J8" s="4">
-        <v>0.3264463468186345</v>
+        <v>0.3139209046269424</v>
       </c>
       <c r="K8" s="4">
         <v>79.2547531833245</v>
@@ -4803,13 +4803,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>71.7948717948718</v>
+        <v>70.51282051282051</v>
       </c>
       <c r="C9" s="3">
         <v>11.53846153846154</v>
       </c>
       <c r="D9" s="3">
-        <v>16.66666666666666</v>
+        <v>17.94871794871795</v>
       </c>
       <c r="E9" s="3">
         <v>1.282051282051282</v>
@@ -4818,16 +4818,16 @@
         <v>15.38461538461539</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>1.282051282051282</v>
       </c>
       <c r="H9" s="4">
-        <v>0.5176084384211607</v>
+        <v>0.521620398314806</v>
       </c>
       <c r="I9" s="4">
-        <v>0.318942235235927</v>
+        <v>0.2795008889921927</v>
       </c>
       <c r="J9" s="4">
-        <v>0.330371639482937</v>
+        <v>0.3310587426022881</v>
       </c>
       <c r="K9" s="4">
         <v>79.73094365951498</v>
@@ -4871,13 +4871,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.372524294868662</v>
+        <v>0.3585668365890062</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3229631669849401</v>
+        <v>0.3027172216473785</v>
       </c>
       <c r="J10" s="4">
-        <v>0.3234314125636826</v>
+        <v>0.2872602819469279</v>
       </c>
       <c r="K10" s="4">
         <v>84.81815803244361</v>
@@ -4921,13 +4921,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.4644273581723621</v>
+        <v>0.4651594839964036</v>
       </c>
       <c r="I11" s="4">
-        <v>0.3514135200493544</v>
+        <v>0.3356444036011628</v>
       </c>
       <c r="J11" s="4">
-        <v>0.3895025109867233</v>
+        <v>0.3665888925756212</v>
       </c>
       <c r="K11" s="4">
         <v>83.61241932670536</v>
@@ -4971,13 +4971,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.4474888270680248</v>
+        <v>0.4411215760273944</v>
       </c>
       <c r="I12" s="4">
-        <v>0.2838346960955881</v>
+        <v>0.2718827007716479</v>
       </c>
       <c r="J12" s="4">
-        <v>0.3295102734661871</v>
+        <v>0.3093908429527945</v>
       </c>
       <c r="K12" s="4">
         <v>82.70320948892387</v>
@@ -5021,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.4578958032359397</v>
+        <v>0.4550750232379344</v>
       </c>
       <c r="I13" s="4">
-        <v>0.308580819844236</v>
+        <v>0.297432749987425</v>
       </c>
       <c r="J13" s="4">
-        <v>0.3514945572329351</v>
+        <v>0.3390982157865901</v>
       </c>
       <c r="K13" s="4">
         <v>79.62279783708311</v>
@@ -5071,13 +5071,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.4454671093303567</v>
+        <v>0.4246448190377519</v>
       </c>
       <c r="I14" s="4">
-        <v>0.3013286484602129</v>
+        <v>0.2902013329697112</v>
       </c>
       <c r="J14" s="4">
-        <v>0.3435002697345537</v>
+        <v>0.3489627205726392</v>
       </c>
       <c r="K14" s="4">
         <v>77.28283621140777</v>
@@ -5121,13 +5121,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.397992929173231</v>
+        <v>0.3812138920778633</v>
       </c>
       <c r="I15" s="4">
-        <v>0.3222549357431434</v>
+        <v>0.305243531445546</v>
       </c>
       <c r="J15" s="4">
-        <v>0.3213914189574074</v>
+        <v>0.3006337508921652</v>
       </c>
       <c r="K15" s="4">
         <v>82.26103261817541</v>
@@ -5171,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.4737855954483662</v>
+        <v>0.4503627223598083</v>
       </c>
       <c r="I16" s="4">
-        <v>0.3017248041469834</v>
+        <v>0.2856205567391952</v>
       </c>
       <c r="J16" s="4">
-        <v>0.3538671018491387</v>
+        <v>0.3578690941186691</v>
       </c>
       <c r="K16" s="4">
         <v>75.69073783359468</v>
@@ -5221,13 +5221,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.3471451869215875</v>
+        <v>0.3380047618488857</v>
       </c>
       <c r="I17" s="4">
-        <v>0.2589870709023719</v>
+        <v>0.2465153397229173</v>
       </c>
       <c r="J17" s="4">
-        <v>0.3031730357504444</v>
+        <v>0.2852369975422738</v>
       </c>
       <c r="K17" s="4">
         <v>84.27655677655621</v>
@@ -6374,13 +6374,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" s="5">
         <v>9</v>
       </c>
       <c r="D9" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" s="5">
         <v>1</v>
@@ -6389,7 +6389,7 @@
         <v>12</v>
       </c>
       <c r="G9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="5">
         <v>1</v>
@@ -6924,16 +6924,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2004704173607698</v>
+        <v>0.2826013820373134</v>
       </c>
       <c r="O3" s="5">
         <v>22</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2929687360582923</v>
+        <v>0.2926128351930434</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.288373348475414</v>
+        <v>0.2804862870277069</v>
       </c>
       <c r="R3" s="5">
         <v>22</v>
@@ -6983,16 +6983,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4526199502244289</v>
+        <v>0.4410210105065744</v>
       </c>
       <c r="O4" s="5">
         <v>13</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5800881864394752</v>
+        <v>0.5765192819109046</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1911601418743267</v>
+        <v>0.190267915742184</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -7042,16 +7042,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4916059510887389</v>
+        <v>0.5547251133129407</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4309103317136674</v>
+        <v>0.43817956134089</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3728146905672257</v>
+        <v>0.369809016175597</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -7224,16 +7224,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3985281152055432</v>
+        <v>0.4726811919317697</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3003933329732034</v>
+        <v>0.2960177127138403</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3068322002872887</v>
+        <v>0.2986618001364335</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -7281,16 +7281,16 @@
         <v>7</v>
       </c>
       <c r="N4" s="4">
-        <v>4.220041084533372</v>
+        <v>4.123075704926805</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>1.429241110759827</v>
+        <v>1.369640144463474</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6210773707571462</v>
+        <v>0.6072251736704938</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -7340,7 +7340,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.6947083700325238</v>
+        <v>0.7537840175781128</v>
       </c>
       <c r="O5" s="5">
         <v>23</v>
@@ -7349,7 +7349,7 @@
         <v>0.3977283575736577</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4039684247048145</v>
+        <v>0.4013999182897889</v>
       </c>
       <c r="R5" s="5">
         <v>23</v>
@@ -7522,16 +7522,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>0.05968238288360524</v>
+        <v>0.2675203806549007</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3480973462382579</v>
+        <v>0.300438850039743</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2565130828885357</v>
+        <v>0.1816803990431481</v>
       </c>
       <c r="R3" s="5">
         <v>20</v>
@@ -7581,16 +7581,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.02203293764961078</v>
+        <v>-0.05397627071772604</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4451696254907534</v>
+        <v>0.4427124460239753</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2989769124134111</v>
+        <v>0.2970978928211691</v>
       </c>
       <c r="R4" s="5">
         <v>17</v>
@@ -7640,16 +7640,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3820196114605438</v>
+        <v>0.3757021746036742</v>
       </c>
       <c r="O5" s="5">
         <v>20</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5975849066531976</v>
+        <v>0.5970989499718999</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4360004895336659</v>
+        <v>0.4360004895336658</v>
       </c>
       <c r="R5" s="5">
         <v>20</v>
@@ -7822,16 +7822,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2396624319842395</v>
+        <v>0.2746000050481996</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2797730439261573</v>
+        <v>0.2764841693321839</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2586901146927918</v>
+        <v>0.2551271672159873</v>
       </c>
       <c r="R3" s="5">
         <v>24</v>
@@ -7881,16 +7881,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3042133747795902</v>
+        <v>0.2981966153081999</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6782266789809671</v>
+        <v>0.6763753683743855</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3503670408241313</v>
+        <v>0.3499659235260386</v>
       </c>
       <c r="R4" s="5">
         <v>15</v>
@@ -7940,16 +7940,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4450761873070587</v>
+        <v>0.6086640154943552</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4818876438075546</v>
+        <v>0.494471322898885</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4158568772248811</v>
+        <v>0.4080669806445336</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -8122,16 +8122,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1098226580043683</v>
+        <v>0.2502891397863323</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.264084007999474</v>
+        <v>0.2463357455942022</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2550651933707127</v>
+        <v>0.2356492523065529</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -8181,16 +8181,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.04771873496634151</v>
+        <v>0.0651407853063688</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4289925153484248</v>
+        <v>0.4276523576299612</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2237720173223998</v>
+        <v>0.22274719083181</v>
       </c>
       <c r="R4" s="5">
         <v>17</v>
@@ -8240,16 +8240,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1756412389029839</v>
+        <v>0.2823220416723444</v>
       </c>
       <c r="O5" s="5">
         <v>24</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4186493427390036</v>
+        <v>0.4044622949466614</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3663479189783363</v>
+        <v>0.3598686841007457</v>
       </c>
       <c r="R5" s="5">
         <v>24</v>
